--- a/grupos/2ARHV - Estadisticos 20232.xlsx
+++ b/grupos/2ARHV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="116">
   <si>
     <t>Materia</t>
   </si>
@@ -215,18 +215,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -239,112 +239,130 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>ENRIQUEZ</t>
+    <t>DE JESUS</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>SOSA</t>
   </si>
   <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>TREJO</t>
   </si>
   <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
   </si>
   <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>LUZ YESENIA</t>
+    <t>NURIA BELEN</t>
   </si>
   <si>
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
-    <t>OSCAR ALEXANDER</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>DORIAN</t>
   </si>
   <si>
     <t>VICTORIA VIANNEY</t>
@@ -912,31 +930,31 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -969,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="AD4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE4">
         <v>8</v>
@@ -981,10 +999,10 @@
         <v>8</v>
       </c>
       <c r="AH4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ4">
         <v>9</v>
@@ -1025,31 +1043,31 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1088,7 +1106,7 @@
         <v>5</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG5">
         <v>5</v>
@@ -1097,7 +1115,7 @@
         <v>5</v>
       </c>
       <c r="AI5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ5">
         <v>5</v>
@@ -1138,31 +1156,31 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1201,16 +1219,16 @@
         <v>7</v>
       </c>
       <c r="AF6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH6">
         <v>5</v>
       </c>
       <c r="AI6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ6">
         <v>5</v>
@@ -1251,31 +1269,31 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1314,7 +1332,7 @@
         <v>5</v>
       </c>
       <c r="AF7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG7">
         <v>8</v>
@@ -1364,31 +1382,31 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1421,19 +1439,19 @@
         <v>6</v>
       </c>
       <c r="AD8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI8">
         <v>9</v>
@@ -1477,31 +1495,31 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1531,7 +1549,7 @@
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD9">
         <v>7</v>
@@ -1540,19 +1558,19 @@
         <v>9</v>
       </c>
       <c r="AF9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK9">
         <v>-1</v>
@@ -1590,31 +1608,31 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1653,7 +1671,7 @@
         <v>6</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG10">
         <v>7</v>
@@ -1662,7 +1680,7 @@
         <v>5</v>
       </c>
       <c r="AI10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ10">
         <v>5</v>
@@ -1703,31 +1721,31 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1760,16 +1778,16 @@
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE11">
         <v>8</v>
       </c>
       <c r="AF11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH11">
         <v>8</v>
@@ -1778,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="AJ11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK11">
         <v>-1</v>
@@ -1816,31 +1834,31 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1885,13 +1903,13 @@
         <v>9</v>
       </c>
       <c r="AH12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI12">
         <v>7</v>
       </c>
       <c r="AJ12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK12">
         <v>-1</v>
@@ -1929,31 +1947,31 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1992,19 +2010,19 @@
         <v>9</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH13">
         <v>8</v>
       </c>
       <c r="AI13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK13">
         <v>-1</v>
@@ -2042,31 +2060,31 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2099,22 +2117,22 @@
         <v>6</v>
       </c>
       <c r="AD14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ14">
         <v>5</v>
@@ -2155,31 +2173,31 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2268,31 +2286,31 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2331,13 +2349,13 @@
         <v>7</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI16">
         <v>5</v>
@@ -2381,31 +2399,31 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2438,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="AD17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE17">
         <v>8</v>
@@ -2450,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="AH17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI17">
         <v>6</v>
@@ -2494,31 +2512,31 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2551,13 +2569,13 @@
         <v>6</v>
       </c>
       <c r="AD18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE18">
         <v>5</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>9</v>
@@ -2607,31 +2625,31 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2670,7 +2688,7 @@
         <v>5</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG19">
         <v>5</v>
@@ -2679,7 +2697,7 @@
         <v>5</v>
       </c>
       <c r="AI19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ19">
         <v>5</v>
@@ -2720,31 +2738,31 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2774,10 +2792,10 @@
         <v>-1</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE20">
         <v>8</v>
@@ -2786,16 +2804,16 @@
         <v>6</v>
       </c>
       <c r="AG20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI20">
         <v>6</v>
       </c>
       <c r="AJ20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK20">
         <v>-1</v>
@@ -2833,31 +2851,31 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2887,13 +2905,13 @@
         <v>-1</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF21">
         <v>10</v>
@@ -2905,10 +2923,10 @@
         <v>7</v>
       </c>
       <c r="AI21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK21">
         <v>-1</v>
@@ -2946,31 +2964,31 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -3009,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>5</v>
@@ -3018,7 +3036,7 @@
         <v>5</v>
       </c>
       <c r="AI22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ22">
         <v>5</v>
@@ -3059,31 +3077,31 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3119,10 +3137,10 @@
         <v>5</v>
       </c>
       <c r="AE23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG23">
         <v>5</v>
@@ -3172,31 +3190,31 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3226,13 +3244,13 @@
         <v>-1</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF24">
         <v>6</v>
@@ -3241,13 +3259,13 @@
         <v>9</v>
       </c>
       <c r="AH24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK24">
         <v>-1</v>
@@ -3285,31 +3303,31 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3342,7 +3360,7 @@
         <v>9</v>
       </c>
       <c r="AD25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE25">
         <v>9</v>
@@ -3351,16 +3369,16 @@
         <v>10</v>
       </c>
       <c r="AG25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI25">
         <v>10</v>
       </c>
       <c r="AJ25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AK25">
         <v>-1</v>
@@ -3377,10 +3395,10 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>-1</v>
@@ -3389,10 +3407,10 @@
         <v>-1</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3427,31 +3445,31 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3481,28 +3499,28 @@
         <v>-1</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE27">
         <v>8</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG27">
         <v>8</v>
       </c>
       <c r="AH27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI27">
         <v>7</v>
       </c>
       <c r="AJ27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK27">
         <v>-1</v>
@@ -3540,31 +3558,31 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3594,25 +3612,25 @@
         <v>-1</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE28">
         <v>8</v>
       </c>
       <c r="AF28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG28">
         <v>8</v>
       </c>
       <c r="AH28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ28">
         <v>8</v>
@@ -3653,31 +3671,31 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3707,28 +3725,28 @@
         <v>-1</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK29">
         <v>-1</v>
@@ -3766,31 +3784,31 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3820,25 +3838,25 @@
         <v>-1</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD30">
         <v>5</v>
       </c>
       <c r="AE30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ30">
         <v>5</v>
@@ -3879,31 +3897,31 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -3936,13 +3954,13 @@
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG31">
         <v>9</v>
@@ -3954,7 +3972,7 @@
         <v>8</v>
       </c>
       <c r="AJ31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK31">
         <v>-1</v>
@@ -3992,31 +4010,31 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -4055,16 +4073,16 @@
         <v>6</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH32">
         <v>5</v>
       </c>
       <c r="AI32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ32">
         <v>5</v>
@@ -4105,31 +4123,31 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -4171,13 +4189,13 @@
         <v>6</v>
       </c>
       <c r="AG33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH33">
         <v>5</v>
       </c>
       <c r="AI33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ33">
         <v>5</v>
@@ -4218,31 +4236,31 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>-1</v>
@@ -4278,19 +4296,19 @@
         <v>5</v>
       </c>
       <c r="AE34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH34">
         <v>5</v>
       </c>
       <c r="AI34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ34">
         <v>5</v>
@@ -4331,31 +4349,31 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>-1</v>
@@ -4391,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="AE35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG35">
         <v>8</v>
       </c>
       <c r="AH35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ35">
         <v>5</v>
@@ -4444,31 +4462,31 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>-1</v>
@@ -4504,10 +4522,10 @@
         <v>5</v>
       </c>
       <c r="AE36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG36">
         <v>6</v>
@@ -4516,7 +4534,7 @@
         <v>5</v>
       </c>
       <c r="AI36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ36">
         <v>5</v>
@@ -4557,31 +4575,31 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
         <v>-1</v>
@@ -4614,22 +4632,22 @@
         <v>5</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE37">
         <v>8</v>
       </c>
       <c r="AF37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH37">
         <v>5</v>
       </c>
       <c r="AI37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ37">
         <v>5</v>
@@ -4816,25 +4834,25 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O4">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="P4">
         <v>93.8</v>
       </c>
       <c r="Q4">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R4">
         <v>95.5</v>
@@ -4843,25 +4861,25 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="X4">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="Y4">
         <v>93.8</v>
       </c>
       <c r="Z4">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA4">
         <v>95.5</v>
@@ -4902,58 +4920,58 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K5">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="L5">
+        <v>87.5</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
         <v>90</v>
       </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>92</v>
-      </c>
       <c r="O5">
-        <v>82.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="Q5">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S5">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T5">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="U5">
+        <v>87.5</v>
+      </c>
+      <c r="V5">
+        <v>100</v>
+      </c>
+      <c r="W5">
         <v>90</v>
       </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-      <c r="W5">
-        <v>92</v>
-      </c>
       <c r="X5">
-        <v>82.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="Y5">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="Z5">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="AB5">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -4988,58 +5006,58 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K6">
-        <v>75</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="O6">
-        <v>74.3</v>
+        <v>80</v>
       </c>
       <c r="P6">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q6">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R6">
-        <v>54.5</v>
+        <v>72.7</v>
       </c>
       <c r="S6">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T6">
-        <v>75</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V6">
         <v>100</v>
       </c>
       <c r="W6">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="X6">
-        <v>74.3</v>
+        <v>80</v>
       </c>
       <c r="Y6">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Z6">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AA6">
-        <v>54.5</v>
+        <v>72.7</v>
       </c>
       <c r="AB6">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -5074,58 +5092,58 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K7">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="L7">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O7">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="R7">
-        <v>95.5</v>
+        <v>81.8</v>
       </c>
       <c r="S7">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T7">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="U7">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="V7">
         <v>100</v>
       </c>
       <c r="W7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X7">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="Y7">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z7">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="AA7">
-        <v>95.5</v>
+        <v>81.8</v>
       </c>
       <c r="AB7">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -5160,7 +5178,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -5172,22 +5190,22 @@
         <v>96</v>
       </c>
       <c r="O8">
-        <v>85.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S8">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -5199,19 +5217,19 @@
         <v>96</v>
       </c>
       <c r="X8">
-        <v>85.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Y8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AA8">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AB8">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -5246,7 +5264,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K9">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L9">
         <v>95</v>
@@ -5255,25 +5273,25 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q9">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S9">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T9">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U9">
         <v>95</v>
@@ -5282,22 +5300,22 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X9">
         <v>100</v>
       </c>
       <c r="Y9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z9">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="AB9">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -5332,58 +5350,58 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K10">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O10">
-        <v>88.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="P10">
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S10">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T10">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X10">
-        <v>88.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="Y10">
         <v>100</v>
       </c>
       <c r="Z10">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="AA10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="AB10">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -5427,19 +5445,19 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O11">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5454,19 +5472,19 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X11">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z11">
         <v>100</v>
       </c>
       <c r="AA11">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="AB11">
         <v>100</v>
@@ -5504,7 +5522,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -5516,23 +5534,23 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P12">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R12">
+        <v>95.5</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>90.90000000000001</v>
       </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
       <c r="U12">
         <v>100</v>
       </c>
@@ -5543,16 +5561,16 @@
         <v>100</v>
       </c>
       <c r="X12">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Y12">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AA12">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AB12">
         <v>100</v>
@@ -5590,7 +5608,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -5602,22 +5620,22 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R13">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T13">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -5629,19 +5647,19 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y13">
         <v>100</v>
       </c>
       <c r="Z13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AA13">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="AB13">
-        <v>100</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -5679,22 +5697,22 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O14">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="P14">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q14">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -5706,22 +5724,22 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="X14">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Y14">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z14">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -5765,55 +5783,55 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="O15">
-        <v>57.1</v>
+        <v>28.6</v>
       </c>
       <c r="P15">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="Q15">
-        <v>56.3</v>
+        <v>28.1</v>
       </c>
       <c r="R15">
-        <v>27.3</v>
+        <v>13.6</v>
       </c>
       <c r="S15">
-        <v>55.6</v>
+        <v>27.8</v>
       </c>
       <c r="T15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X15">
-        <v>57.1</v>
+        <v>28.6</v>
       </c>
       <c r="Y15">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="Z15">
-        <v>56.3</v>
+        <v>28.1</v>
       </c>
       <c r="AA15">
-        <v>27.3</v>
+        <v>13.6</v>
       </c>
       <c r="AB15">
-        <v>55.6</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -5848,22 +5866,22 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O16">
-        <v>85.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -5872,25 +5890,25 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="X16">
-        <v>85.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Y16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z16">
         <v>100</v>
@@ -5899,7 +5917,7 @@
         <v>100</v>
       </c>
       <c r="AB16">
-        <v>100</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="17" spans="1:28">
@@ -5934,7 +5952,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5943,10 +5961,10 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O17">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -5961,7 +5979,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -5970,10 +5988,10 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X17">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -6020,7 +6038,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -6029,16 +6047,16 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -6047,7 +6065,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6056,16 +6074,16 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X18">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Y18">
         <v>100</v>
       </c>
       <c r="Z18">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA18">
         <v>100</v>
@@ -6106,7 +6124,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="L19">
         <v>90</v>
@@ -6115,25 +6133,25 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O19">
-        <v>85.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P19">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q19">
         <v>68.8</v>
       </c>
       <c r="R19">
-        <v>90.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T19">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="U19">
         <v>90</v>
@@ -6142,22 +6160,22 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="X19">
-        <v>85.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Y19">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Z19">
         <v>68.8</v>
       </c>
       <c r="AA19">
-        <v>90.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="AB19">
-        <v>100</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="20" spans="1:28">
@@ -6192,25 +6210,25 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O20">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="P20">
         <v>93.8</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -6219,25 +6237,25 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="X20">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Y20">
         <v>93.8</v>
       </c>
       <c r="Z20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA20">
         <v>100</v>
@@ -6278,10 +6296,10 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -6290,25 +6308,25 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="P21">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S21">
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -6317,16 +6335,16 @@
         <v>100</v>
       </c>
       <c r="X21">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Y21">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Z21">
         <v>100</v>
       </c>
       <c r="AA21">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -6364,55 +6382,55 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>91.7</v>
+        <v>81.8</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O22">
-        <v>88.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P22">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q22">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="R22">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>91.7</v>
+        <v>81.8</v>
       </c>
       <c r="U22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="X22">
-        <v>88.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Y22">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Z22">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="AA22">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="AB22">
         <v>100</v>
@@ -6450,58 +6468,58 @@
         <v>55.6</v>
       </c>
       <c r="K23">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="L23">
-        <v>85</v>
+        <v>42.5</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="O23">
-        <v>71.40000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="P23">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="Q23">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="R23">
-        <v>68.2</v>
+        <v>34.1</v>
       </c>
       <c r="S23">
-        <v>55.6</v>
+        <v>27.8</v>
       </c>
       <c r="T23">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="U23">
-        <v>85</v>
+        <v>42.5</v>
       </c>
       <c r="V23">
         <v>100</v>
       </c>
       <c r="W23">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="X23">
-        <v>71.40000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="Y23">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="Z23">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="AA23">
-        <v>68.2</v>
+        <v>34.1</v>
       </c>
       <c r="AB23">
-        <v>55.6</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="24" spans="1:28">
@@ -6536,58 +6554,58 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K24">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L24">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O24">
-        <v>82.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q24">
         <v>93.8</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S24">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T24">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U24">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X24">
-        <v>82.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Y24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Z24">
         <v>93.8</v>
       </c>
       <c r="AA24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="AB24">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:28">
@@ -6690,13 +6708,13 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W26">
         <v>100</v>
       </c>
       <c r="X26">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:28">
@@ -6731,10 +6749,10 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="L27">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -6743,25 +6761,25 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P27">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R27">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="U27">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -6770,16 +6788,16 @@
         <v>100</v>
       </c>
       <c r="X27">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Y27">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Z27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AA27">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AB27">
         <v>100</v>
@@ -6826,19 +6844,19 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O28">
-        <v>91.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R28">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -6853,19 +6871,19 @@
         <v>100</v>
       </c>
       <c r="W28">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X28">
-        <v>91.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="Y28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AA28">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="AB28">
         <v>100</v>
@@ -6903,10 +6921,10 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -6915,14 +6933,14 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="P29">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Q29">
         <v>93.8</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
       <c r="R29">
         <v>100</v>
       </c>
@@ -6930,10 +6948,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6942,13 +6960,13 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="Y29">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Z29">
         <v>93.8</v>
-      </c>
-      <c r="Z29">
-        <v>100</v>
       </c>
       <c r="AA29">
         <v>100</v>
@@ -6989,55 +7007,55 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L30">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M30">
         <v>100</v>
       </c>
       <c r="N30">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="P30">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q30">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R30">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="S30">
         <v>100</v>
       </c>
       <c r="T30">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U30">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="V30">
         <v>100</v>
       </c>
       <c r="W30">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="X30">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="Y30">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z30">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA30">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="AB30">
         <v>100</v>
@@ -7075,7 +7093,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -7084,25 +7102,25 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O31">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P31">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="S31">
         <v>100</v>
       </c>
       <c r="T31">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7111,19 +7129,19 @@
         <v>100</v>
       </c>
       <c r="W31">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X31">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Y31">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z31">
         <v>100</v>
       </c>
       <c r="AA31">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="AB31">
         <v>100</v>
@@ -7161,7 +7179,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>75</v>
+        <v>63.6</v>
       </c>
       <c r="L32">
         <v>75</v>
@@ -7173,22 +7191,22 @@
         <v>96</v>
       </c>
       <c r="O32">
-        <v>97.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P32">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T32">
-        <v>75</v>
+        <v>63.6</v>
       </c>
       <c r="U32">
         <v>75</v>
@@ -7200,19 +7218,19 @@
         <v>96</v>
       </c>
       <c r="X32">
-        <v>97.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="Y32">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AB32">
-        <v>100</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -7247,10 +7265,10 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L33">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -7259,25 +7277,25 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>94.3</v>
+        <v>85.7</v>
       </c>
       <c r="P33">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R33">
-        <v>90.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U33">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -7286,19 +7304,19 @@
         <v>100</v>
       </c>
       <c r="X33">
-        <v>94.3</v>
+        <v>85.7</v>
       </c>
       <c r="Y33">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA33">
-        <v>90.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AB33">
-        <v>100</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="34" spans="1:28">
@@ -7333,7 +7351,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K34">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -7342,25 +7360,25 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O34">
-        <v>85.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P34">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>90.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S34">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T34">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -7369,22 +7387,22 @@
         <v>100</v>
       </c>
       <c r="W34">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X34">
-        <v>85.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Y34">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z34">
         <v>100</v>
       </c>
       <c r="AA34">
-        <v>90.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AB34">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:28">
@@ -7419,7 +7437,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -7428,13 +7446,13 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="P35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -7446,7 +7464,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -7455,13 +7473,13 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="Y35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z35">
         <v>100</v>
@@ -7505,58 +7523,58 @@
         <v>88.90000000000001</v>
       </c>
       <c r="K36">
+        <v>68.2</v>
+      </c>
+      <c r="L36">
+        <v>80</v>
+      </c>
+      <c r="M36">
+        <v>100</v>
+      </c>
+      <c r="N36">
+        <v>98</v>
+      </c>
+      <c r="O36">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="P36">
         <v>75</v>
       </c>
-      <c r="L36">
-        <v>85</v>
-      </c>
-      <c r="M36">
-        <v>100</v>
-      </c>
-      <c r="N36">
-        <v>96</v>
-      </c>
-      <c r="O36">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="P36">
-        <v>81.3</v>
-      </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="S36">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T36">
+        <v>68.2</v>
+      </c>
+      <c r="U36">
+        <v>80</v>
+      </c>
+      <c r="V36">
+        <v>100</v>
+      </c>
+      <c r="W36">
+        <v>98</v>
+      </c>
+      <c r="X36">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="Y36">
         <v>75</v>
       </c>
-      <c r="U36">
-        <v>85</v>
-      </c>
-      <c r="V36">
-        <v>100</v>
-      </c>
-      <c r="W36">
-        <v>96</v>
-      </c>
-      <c r="X36">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="Y36">
-        <v>81.3</v>
-      </c>
       <c r="Z36">
         <v>100</v>
       </c>
       <c r="AA36">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="AB36">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:28">
@@ -7591,58 +7609,58 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M37">
         <v>100</v>
       </c>
       <c r="N37">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="P37">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q37">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T37">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U37">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="V37">
         <v>100</v>
       </c>
       <c r="W37">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="X37">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="Y37">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z37">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AA37">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="AB37">
-        <v>100</v>
+        <v>91.7</v>
       </c>
     </row>
   </sheetData>
@@ -7737,19 +7755,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>24.2</v>
+        <v>39.4</v>
       </c>
       <c r="G3" s="2">
-        <v>75.8</v>
+        <v>60.6</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7769,19 +7787,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2">
-        <v>42.4</v>
+        <v>54.5</v>
       </c>
       <c r="G4" s="2">
-        <v>57.6</v>
+        <v>45.5</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7813,7 +7831,7 @@
         <v>42.4</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7845,7 +7863,7 @@
         <v>33.3</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7856,28 +7874,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2">
-        <v>82.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="G7" s="2">
-        <v>17.6</v>
+        <v>33.3</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7888,28 +7906,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2">
-        <v>84.8</v>
+        <v>73.5</v>
       </c>
       <c r="G8" s="2">
-        <v>15.2</v>
+        <v>26.5</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7920,28 +7938,28 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2">
-        <v>87.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>12.1</v>
+        <v>20.6</v>
       </c>
       <c r="H9">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7952,28 +7970,28 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
       </c>
       <c r="C10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2">
-        <v>97.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="G10" s="2">
-        <v>2.9</v>
+        <v>15.2</v>
       </c>
       <c r="H10">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -8023,7 +8041,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8055,16 +8073,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920240</v>
+        <v>23330051920226</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -8078,16 +8096,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920240</v>
+        <v>23330051920226</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -8107,10 +8125,10 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -8130,10 +8148,10 @@
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -8147,16 +8165,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920328</v>
+        <v>23330051920333</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -8170,16 +8188,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920328</v>
+        <v>23330051920333</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -8193,39 +8211,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920260</v>
+        <v>23330051920213</v>
       </c>
       <c r="B8" t="s">
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920260</v>
+        <v>23330051920227</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -8239,39 +8257,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920278</v>
+        <v>23330051920242</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920278</v>
+        <v>23330051920240</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -8285,16 +8303,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920213</v>
+        <v>23330051920239</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -8308,16 +8326,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920227</v>
+        <v>23330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -8331,16 +8349,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920239</v>
+        <v>23330051920256</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
@@ -8354,16 +8372,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920256</v>
+        <v>23330051920257</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -8377,16 +8395,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920257</v>
+        <v>23330051920260</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
@@ -8403,13 +8421,13 @@
         <v>23330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -8426,13 +8444,13 @@
         <v>23330051920270</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -8446,16 +8464,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920276</v>
+        <v>23330051920207</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -8464,6 +8482,29 @@
         <v>61</v>
       </c>
       <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920276</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20232.xlsx
+++ b/grupos/2ARHV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="136">
   <si>
     <t>Materia</t>
   </si>
@@ -206,24 +206,24 @@
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -239,33 +239,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MEJIA</t>
   </si>
   <si>
@@ -281,18 +296,39 @@
     <t>ROSALES</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
     <t>BERMUDEZ</t>
   </si>
   <si>
-    <t>GUZMAN</t>
+    <t>TEMOXTLE</t>
   </si>
   <si>
     <t>VILLA</t>
   </si>
   <si>
+    <t>FERRER</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -302,9 +338,6 @@
     <t>RICO</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>CANDELARIO</t>
   </si>
   <si>
@@ -314,39 +347,60 @@
     <t>TREJO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>YAMILETH</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
     <t>LUZ YESENIA</t>
   </si>
   <si>
     <t>SILVANA</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
+    <t>XIMENA ISABEL</t>
   </si>
   <si>
     <t>NURIA BELEN</t>
   </si>
   <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
     <t>DANNA PAOLA</t>
   </si>
   <si>
@@ -366,6 +420,12 @@
   </si>
   <si>
     <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -957,34 +1017,34 @@
         <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>9</v>
@@ -993,7 +1053,7 @@
         <v>8</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>8</v>
@@ -1070,40 +1130,40 @@
         <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>5</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF5">
         <v>5</v>
@@ -1183,55 +1243,55 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>6</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE6">
         <v>7</v>
       </c>
       <c r="AF6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK6">
         <v>-1</v>
@@ -1296,55 +1356,55 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>5</v>
       </c>
       <c r="AD7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG7">
         <v>8</v>
       </c>
       <c r="AH7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI7">
         <v>5</v>
       </c>
       <c r="AJ7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK7">
         <v>-1</v>
@@ -1409,37 +1469,37 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC8">
         <v>6</v>
       </c>
       <c r="AD8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE8">
         <v>7</v>
@@ -1454,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="AI8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8">
         <v>-1</v>
@@ -1522,43 +1582,43 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>7</v>
       </c>
       <c r="AD9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE9">
         <v>9</v>
       </c>
       <c r="AF9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG9">
         <v>9</v>
@@ -1635,37 +1695,37 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>6</v>
       </c>
       <c r="AD10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10">
         <v>6</v>
@@ -1677,13 +1737,13 @@
         <v>7</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK10">
         <v>-1</v>
@@ -1748,43 +1808,43 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11">
         <v>8</v>
       </c>
       <c r="AF11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11">
         <v>9</v>
@@ -1861,31 +1921,31 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1897,19 +1957,19 @@
         <v>6</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>9</v>
       </c>
       <c r="AH12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI12">
         <v>7</v>
       </c>
       <c r="AJ12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK12">
         <v>-1</v>
@@ -1974,31 +2034,31 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -2010,19 +2070,19 @@
         <v>9</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK13">
         <v>-1</v>
@@ -2087,43 +2147,43 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>6</v>
       </c>
       <c r="AD14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE14">
         <v>7</v>
       </c>
       <c r="AF14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG14">
         <v>8</v>
@@ -2135,7 +2195,7 @@
         <v>7</v>
       </c>
       <c r="AJ14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK14">
         <v>-1</v>
@@ -2200,31 +2260,31 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -2233,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF15">
         <v>5</v>
@@ -2313,55 +2373,55 @@
         <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>5</v>
       </c>
       <c r="AD16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE16">
         <v>7</v>
       </c>
       <c r="AF16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK16">
         <v>-1</v>
@@ -2426,31 +2486,31 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2462,19 +2522,19 @@
         <v>8</v>
       </c>
       <c r="AF17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG17">
         <v>9</v>
       </c>
       <c r="AH17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK17">
         <v>-1</v>
@@ -2539,31 +2599,31 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2572,7 +2632,7 @@
         <v>8</v>
       </c>
       <c r="AE18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF18">
         <v>7</v>
@@ -2581,13 +2641,13 @@
         <v>9</v>
       </c>
       <c r="AH18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI18">
         <v>7</v>
       </c>
       <c r="AJ18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK18">
         <v>-1</v>
@@ -2652,28 +2712,28 @@
         <v>5</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>-1</v>
@@ -2682,10 +2742,10 @@
         <v>5</v>
       </c>
       <c r="AD19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF19">
         <v>5</v>
@@ -2765,37 +2825,37 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>6</v>
       </c>
       <c r="AD20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE20">
         <v>8</v>
@@ -2807,13 +2867,13 @@
         <v>7</v>
       </c>
       <c r="AH20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK20">
         <v>-1</v>
@@ -2878,55 +2938,55 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>7</v>
       </c>
       <c r="AD21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE21">
         <v>9</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>8</v>
       </c>
       <c r="AH21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK21">
         <v>-1</v>
@@ -2991,37 +3051,37 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>5</v>
       </c>
       <c r="AD22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE22">
         <v>6</v>
@@ -3030,16 +3090,16 @@
         <v>7</v>
       </c>
       <c r="AG22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK22">
         <v>-1</v>
@@ -3104,31 +3164,31 @@
         <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -3217,37 +3277,37 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>7</v>
       </c>
       <c r="AD24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE24">
         <v>8</v>
@@ -3259,7 +3319,7 @@
         <v>9</v>
       </c>
       <c r="AH24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI24">
         <v>8</v>
@@ -3330,31 +3390,31 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -3401,10 +3461,10 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF26">
         <v>8</v>
@@ -3472,31 +3532,31 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>7</v>
@@ -3585,43 +3645,43 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC28">
         <v>7</v>
       </c>
       <c r="AD28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE28">
         <v>8</v>
       </c>
       <c r="AF28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG28">
         <v>8</v>
@@ -3698,31 +3758,31 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>7</v>
@@ -3734,10 +3794,10 @@
         <v>7</v>
       </c>
       <c r="AF29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH29">
         <v>7</v>
@@ -3746,7 +3806,7 @@
         <v>8</v>
       </c>
       <c r="AJ29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK29">
         <v>-1</v>
@@ -3811,37 +3871,37 @@
         <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC30">
         <v>6</v>
       </c>
       <c r="AD30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30">
         <v>8</v>
@@ -3850,7 +3910,7 @@
         <v>6</v>
       </c>
       <c r="AG30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH30">
         <v>7</v>
@@ -3859,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="AJ30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK30">
         <v>-1</v>
@@ -3924,31 +3984,31 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -3957,10 +4017,10 @@
         <v>9</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG31">
         <v>9</v>
@@ -3972,7 +4032,7 @@
         <v>8</v>
       </c>
       <c r="AJ31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK31">
         <v>-1</v>
@@ -4037,52 +4097,52 @@
         <v>5</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC32">
         <v>5</v>
       </c>
       <c r="AD32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE32">
         <v>6</v>
       </c>
       <c r="AF32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH32">
         <v>5</v>
       </c>
       <c r="AI32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ32">
         <v>5</v>
@@ -4150,37 +4210,37 @@
         <v>5</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>5</v>
       </c>
       <c r="AD33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE33">
         <v>8</v>
@@ -4195,7 +4255,7 @@
         <v>5</v>
       </c>
       <c r="AI33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ33">
         <v>5</v>
@@ -4263,55 +4323,55 @@
         <v>10</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC34">
         <v>6</v>
       </c>
       <c r="AD34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE34">
         <v>7</v>
       </c>
       <c r="AF34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG34">
         <v>7</v>
       </c>
       <c r="AH34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI34">
         <v>7</v>
       </c>
       <c r="AJ34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK34">
         <v>-1</v>
@@ -4376,37 +4436,37 @@
         <v>10</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC35">
         <v>6</v>
       </c>
       <c r="AD35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE35">
         <v>7</v>
@@ -4418,13 +4478,13 @@
         <v>8</v>
       </c>
       <c r="AH35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI35">
         <v>7</v>
       </c>
       <c r="AJ35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK35">
         <v>-1</v>
@@ -4489,37 +4549,37 @@
         <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC36">
         <v>5</v>
       </c>
       <c r="AD36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE36">
         <v>7</v>
@@ -4534,7 +4594,7 @@
         <v>5</v>
       </c>
       <c r="AI36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ36">
         <v>5</v>
@@ -4602,37 +4662,37 @@
         <v>5</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC37">
         <v>5</v>
       </c>
       <c r="AD37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE37">
         <v>8</v>
@@ -4644,13 +4704,13 @@
         <v>6</v>
       </c>
       <c r="AH37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK37">
         <v>-1</v>
@@ -4861,28 +4921,28 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U4">
+        <v>98.3</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+      <c r="W4">
         <v>97.5</v>
       </c>
-      <c r="V4">
-        <v>100</v>
-      </c>
-      <c r="W4">
-        <v>96</v>
-      </c>
       <c r="X4">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="Y4">
         <v>93.8</v>
       </c>
       <c r="Z4">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AA4">
         <v>96.90000000000001</v>
-      </c>
-      <c r="AA4">
-        <v>95.5</v>
       </c>
       <c r="AB4">
         <v>100</v>
@@ -4947,31 +5007,31 @@
         <v>86.09999999999999</v>
       </c>
       <c r="T5">
-        <v>72.7</v>
+        <v>81.3</v>
       </c>
       <c r="U5">
-        <v>87.5</v>
+        <v>88.3</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="X5">
-        <v>70</v>
+        <v>63.4</v>
       </c>
       <c r="Y5">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="Z5">
-        <v>90.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="AA5">
-        <v>88.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="AB5">
-        <v>86.09999999999999</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -5033,31 +5093,31 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T6">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U6">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="V6">
         <v>100</v>
       </c>
       <c r="W6">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X6">
-        <v>80</v>
+        <v>84.8</v>
       </c>
       <c r="Y6">
-        <v>78.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z6">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AA6">
-        <v>72.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AB6">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -5119,31 +5179,31 @@
         <v>86.09999999999999</v>
       </c>
       <c r="T7">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U7">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="V7">
         <v>100</v>
       </c>
       <c r="W7">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X7">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Y7">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z7">
-        <v>68.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AA7">
-        <v>81.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AB7">
-        <v>86.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -5205,7 +5265,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T8">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -5214,22 +5274,22 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="X8">
-        <v>91.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Y8">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="Z8">
+        <v>91.7</v>
+      </c>
+      <c r="AA8">
         <v>96.90000000000001</v>
       </c>
-      <c r="Z8">
-        <v>93.8</v>
-      </c>
-      <c r="AA8">
-        <v>90.90000000000001</v>
-      </c>
       <c r="AB8">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -5291,31 +5351,31 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T9">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U9">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V9">
         <v>100</v>
       </c>
       <c r="W9">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X9">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Y9">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z9">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AA9">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="AB9">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -5377,31 +5437,31 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T10">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U10">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X10">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="Y10">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z10">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="AA10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB10">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -5463,7 +5523,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -5472,19 +5532,19 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X11">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="Y11">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="AA11">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AB11">
         <v>100</v>
@@ -5549,7 +5609,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -5561,16 +5621,16 @@
         <v>100</v>
       </c>
       <c r="X12">
-        <v>98.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="Y12">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z12">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="AA12">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB12">
         <v>100</v>
@@ -5635,7 +5695,7 @@
         <v>91.7</v>
       </c>
       <c r="T13">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -5647,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>92.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -5656,10 +5716,10 @@
         <v>93.8</v>
       </c>
       <c r="AA13">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB13">
-        <v>91.7</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -5721,25 +5781,25 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="U14">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="X14">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="Y14">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z14">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -5810,28 +5870,28 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="X15">
-        <v>28.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z15">
-        <v>28.1</v>
+        <v>18.8</v>
       </c>
       <c r="AA15">
-        <v>13.6</v>
+        <v>9.4</v>
       </c>
       <c r="AB15">
-        <v>27.8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -5893,31 +5953,31 @@
         <v>91.7</v>
       </c>
       <c r="T16">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U16">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>96</v>
+        <v>91.3</v>
       </c>
       <c r="X16">
-        <v>87.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Y16">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="Z16">
+        <v>93.8</v>
+      </c>
+      <c r="AA16">
         <v>96.90000000000001</v>
       </c>
-      <c r="Z16">
-        <v>100</v>
-      </c>
-      <c r="AA16">
-        <v>100</v>
-      </c>
       <c r="AB16">
-        <v>91.7</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:28">
@@ -5979,7 +6039,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>95.5</v>
+        <v>87.5</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -5988,19 +6048,19 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X17">
         <v>92.90000000000001</v>
       </c>
       <c r="Y17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Z17">
         <v>100</v>
       </c>
       <c r="AA17">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB17">
         <v>100</v>
@@ -6065,7 +6125,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6074,16 +6134,16 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X18">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="Y18">
         <v>100</v>
       </c>
       <c r="Z18">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AA18">
         <v>100</v>
@@ -6151,7 +6211,7 @@
         <v>91.7</v>
       </c>
       <c r="T19">
-        <v>77.3</v>
+        <v>53.1</v>
       </c>
       <c r="U19">
         <v>90</v>
@@ -6160,22 +6220,22 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="X19">
-        <v>71.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="Y19">
-        <v>78.09999999999999</v>
+        <v>56.3</v>
       </c>
       <c r="Z19">
-        <v>68.8</v>
+        <v>56.3</v>
       </c>
       <c r="AA19">
-        <v>79.5</v>
+        <v>62.5</v>
       </c>
       <c r="AB19">
-        <v>91.7</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="20" spans="1:28">
@@ -6237,25 +6297,25 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U20">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="X20">
-        <v>85.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Y20">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z20">
-        <v>96.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AA20">
         <v>100</v>
@@ -6323,10 +6383,10 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U21">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -6335,16 +6395,16 @@
         <v>100</v>
       </c>
       <c r="X21">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="Y21">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="Z21">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="AA21">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -6409,28 +6469,28 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="U22">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="X22">
-        <v>87.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Y22">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z22">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="AA22">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AB22">
         <v>100</v>
@@ -6495,31 +6555,31 @@
         <v>27.8</v>
       </c>
       <c r="T23">
-        <v>27.3</v>
+        <v>18.8</v>
       </c>
       <c r="U23">
-        <v>42.5</v>
+        <v>53.3</v>
       </c>
       <c r="V23">
         <v>100</v>
       </c>
       <c r="W23">
-        <v>46</v>
+        <v>66.3</v>
       </c>
       <c r="X23">
-        <v>35.7</v>
+        <v>22.3</v>
       </c>
       <c r="Y23">
-        <v>31.3</v>
+        <v>20.8</v>
       </c>
       <c r="Z23">
-        <v>31.3</v>
+        <v>20.8</v>
       </c>
       <c r="AA23">
-        <v>34.1</v>
+        <v>23.4</v>
       </c>
       <c r="AB23">
-        <v>27.8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="24" spans="1:28">
@@ -6581,31 +6641,31 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T24">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U24">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X24">
         <v>85.7</v>
       </c>
       <c r="Y24">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z24">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="AA24">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB24">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:28">
@@ -6714,7 +6774,7 @@
         <v>100</v>
       </c>
       <c r="X26">
-        <v>92.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:28">
@@ -6776,10 +6836,10 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="U27">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -6788,16 +6848,16 @@
         <v>100</v>
       </c>
       <c r="X27">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="Y27">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z27">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="AA27">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB27">
         <v>100</v>
@@ -6871,19 +6931,19 @@
         <v>100</v>
       </c>
       <c r="W28">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X28">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y28">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="Z28">
+        <v>87.5</v>
+      </c>
+      <c r="AA28">
         <v>96.90000000000001</v>
-      </c>
-      <c r="Z28">
-        <v>93.8</v>
-      </c>
-      <c r="AA28">
-        <v>93.2</v>
       </c>
       <c r="AB28">
         <v>100</v>
@@ -6948,10 +7008,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U29">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6960,13 +7020,13 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>94.3</v>
+        <v>92</v>
       </c>
       <c r="Y29">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="Z29">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="AA29">
         <v>100</v>
@@ -7034,28 +7094,28 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U30">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="V30">
         <v>100</v>
       </c>
       <c r="W30">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="X30">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="Y30">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z30">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA30">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AB30">
         <v>100</v>
@@ -7120,7 +7180,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7129,19 +7189,19 @@
         <v>100</v>
       </c>
       <c r="W31">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X31">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Y31">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="AA31">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AB31">
         <v>100</v>
@@ -7206,31 +7266,31 @@
         <v>91.7</v>
       </c>
       <c r="T32">
-        <v>63.6</v>
+        <v>75</v>
       </c>
       <c r="U32">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="V32">
         <v>100</v>
       </c>
       <c r="W32">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="X32">
-        <v>90</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Y32">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z32">
-        <v>96.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AA32">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="AB32">
-        <v>91.7</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -7292,10 +7352,10 @@
         <v>91.7</v>
       </c>
       <c r="T33">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U33">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -7307,16 +7367,16 @@
         <v>85.7</v>
       </c>
       <c r="Y33">
-        <v>84.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Z33">
-        <v>96.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="AA33">
-        <v>86.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="AB33">
-        <v>91.7</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:28">
@@ -7378,7 +7438,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T34">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -7387,22 +7447,22 @@
         <v>100</v>
       </c>
       <c r="W34">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X34">
-        <v>87.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Y34">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z34">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="AA34">
-        <v>86.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="AB34">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:28">
@@ -7464,7 +7524,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -7473,19 +7533,19 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X35">
-        <v>95.7</v>
+        <v>92</v>
       </c>
       <c r="Y35">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="Z35">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AA35">
         <v>96.90000000000001</v>
-      </c>
-      <c r="Z35">
-        <v>100</v>
-      </c>
-      <c r="AA35">
-        <v>100</v>
       </c>
       <c r="AB35">
         <v>100</v>
@@ -7550,31 +7610,31 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T36">
-        <v>68.2</v>
+        <v>75</v>
       </c>
       <c r="U36">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="V36">
         <v>100</v>
       </c>
       <c r="W36">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X36">
-        <v>78.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="Y36">
-        <v>75</v>
+        <v>58.3</v>
       </c>
       <c r="Z36">
-        <v>100</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AA36">
-        <v>81.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AB36">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:28">
@@ -7636,31 +7696,31 @@
         <v>91.7</v>
       </c>
       <c r="T37">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U37">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="V37">
         <v>100</v>
       </c>
       <c r="W37">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="X37">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y37">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z37">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AA37">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AB37">
-        <v>91.7</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7746,7 +7806,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -7755,19 +7815,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>39.4</v>
+        <v>66.7</v>
       </c>
       <c r="G3" s="2">
-        <v>60.6</v>
+        <v>33.3</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7781,25 +7841,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>33</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>54.5</v>
+        <v>78.8</v>
       </c>
       <c r="G4" s="2">
-        <v>45.5</v>
+        <v>21.2</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7810,7 +7870,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -7819,19 +7879,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>57.6</v>
+        <v>78.8</v>
       </c>
       <c r="G5" s="2">
-        <v>42.4</v>
+        <v>21.2</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7842,7 +7902,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -7851,19 +7911,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="G6" s="2">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="H6">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7874,25 +7934,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>66.7</v>
+        <v>88.2</v>
       </c>
       <c r="G7" s="2">
-        <v>33.3</v>
+        <v>11.8</v>
       </c>
       <c r="H7">
         <v>6.8</v>
@@ -7915,19 +7975,19 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>73.5</v>
+        <v>88.2</v>
       </c>
       <c r="G8" s="2">
-        <v>26.5</v>
+        <v>11.8</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7938,28 +7998,28 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
-        <v>79.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>20.6</v>
+        <v>6.1</v>
       </c>
       <c r="H9">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7979,19 +8039,19 @@
         <v>33</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>84.8</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -8041,7 +8101,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8073,19 +8133,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920226</v>
+        <v>23330051920191</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
@@ -8096,16 +8156,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920226</v>
+        <v>23330051920191</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -8119,22 +8179,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920244</v>
+        <v>23330051920328</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8142,16 +8202,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920244</v>
+        <v>23330051920328</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -8165,19 +8225,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920333</v>
+        <v>23330051920357</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
@@ -8188,16 +8248,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920333</v>
+        <v>23330051920357</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -8211,39 +8271,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920213</v>
+        <v>23330051920280</v>
       </c>
       <c r="B8" t="s">
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920227</v>
+        <v>23330051920280</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -8257,16 +8317,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920242</v>
+        <v>23330051920213</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -8280,16 +8340,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920240</v>
+        <v>23330051920226</v>
       </c>
       <c r="B11" t="s">
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -8303,16 +8363,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920239</v>
+        <v>23330051920215</v>
       </c>
       <c r="B12" t="s">
         <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -8326,16 +8386,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920328</v>
+        <v>23330051920227</v>
       </c>
       <c r="B13" t="s">
         <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -8349,16 +8409,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920256</v>
+        <v>23330051920237</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
@@ -8372,16 +8432,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920257</v>
+        <v>23330051920242</v>
       </c>
       <c r="B15" t="s">
         <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -8395,16 +8455,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920260</v>
+        <v>23330051920240</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
@@ -8418,16 +8478,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920330</v>
+        <v>23330051920244</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -8441,16 +8501,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920270</v>
+        <v>23330051920333</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -8464,16 +8524,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920207</v>
+        <v>23330051920252</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -8487,16 +8547,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920276</v>
+        <v>23330051920239</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
@@ -8505,6 +8565,236 @@
         <v>61</v>
       </c>
       <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920256</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920257</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920260</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920330</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920270</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920207</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920327</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920276</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920278</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920277</v>
+      </c>
+      <c r="B30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20232.xlsx
+++ b/grupos/2ARHV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -203,18 +203,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -239,6 +239,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -251,109 +254,16 @@
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
+    <t>ANGEL JESUS</t>
   </si>
   <si>
     <t>DIEGO DE JESUS</t>
@@ -366,66 +276,6 @@
   </si>
   <si>
     <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>SILVANA</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>DORIAN</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>OSCAR ALEXANDER</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +918,7 @@
         <v>9</v>
       </c>
       <c r="AK4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1181,7 +1031,7 @@
         <v>5</v>
       </c>
       <c r="AK5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1294,7 +1144,7 @@
         <v>6</v>
       </c>
       <c r="AK6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1407,7 +1257,7 @@
         <v>6</v>
       </c>
       <c r="AK7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1520,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="AK8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1633,7 +1483,7 @@
         <v>7</v>
       </c>
       <c r="AK9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1746,7 +1596,7 @@
         <v>6</v>
       </c>
       <c r="AK10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1859,7 +1709,7 @@
         <v>8</v>
       </c>
       <c r="AK11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1972,7 +1822,7 @@
         <v>7</v>
       </c>
       <c r="AK12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2085,7 +1935,7 @@
         <v>8</v>
       </c>
       <c r="AK13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2198,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="AK14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2311,7 +2161,7 @@
         <v>5</v>
       </c>
       <c r="AK15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2424,7 +2274,7 @@
         <v>6</v>
       </c>
       <c r="AK16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2537,7 +2387,7 @@
         <v>7</v>
       </c>
       <c r="AK17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2650,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="AK18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2763,7 +2613,7 @@
         <v>5</v>
       </c>
       <c r="AK19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2876,7 +2726,7 @@
         <v>7</v>
       </c>
       <c r="AK20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2989,7 +2839,7 @@
         <v>8</v>
       </c>
       <c r="AK21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3102,7 +2952,7 @@
         <v>6</v>
       </c>
       <c r="AK22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3215,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="AK23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3328,7 +3178,7 @@
         <v>9</v>
       </c>
       <c r="AK24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3441,7 +3291,7 @@
         <v>8</v>
       </c>
       <c r="AK25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3583,7 +3433,7 @@
         <v>8</v>
       </c>
       <c r="AK27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3696,7 +3546,7 @@
         <v>8</v>
       </c>
       <c r="AK28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3809,7 +3659,7 @@
         <v>7</v>
       </c>
       <c r="AK29">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -3922,7 +3772,7 @@
         <v>7</v>
       </c>
       <c r="AK30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4035,7 +3885,7 @@
         <v>8</v>
       </c>
       <c r="AK31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4148,7 +3998,7 @@
         <v>5</v>
       </c>
       <c r="AK32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4261,7 +4111,7 @@
         <v>5</v>
       </c>
       <c r="AK33">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -4374,7 +4224,7 @@
         <v>6</v>
       </c>
       <c r="AK34">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -4487,7 +4337,7 @@
         <v>6</v>
       </c>
       <c r="AK35">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -4600,7 +4450,7 @@
         <v>5</v>
       </c>
       <c r="AK36">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -4713,7 +4563,7 @@
         <v>6</v>
       </c>
       <c r="AK37">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7777,7 +7627,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -7786,27 +7636,30 @@
         <v>33</v>
       </c>
       <c r="D2">
+        <v>22</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>66.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>33.3</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>33</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -7815,19 +7668,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>66.7</v>
+        <v>78.8</v>
       </c>
       <c r="G3" s="2">
-        <v>33.3</v>
+        <v>21.2</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7838,10 +7691,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>33</v>
@@ -7859,7 +7712,7 @@
         <v>21.2</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7870,7 +7723,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -7879,19 +7732,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>78.8</v>
+        <v>81.8</v>
       </c>
       <c r="G5" s="2">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7902,7 +7755,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -7911,19 +7764,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8101,7 +7954,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8133,22 +7986,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920191</v>
+        <v>23330051920216</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8156,45 +8009,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920191</v>
+        <v>23330051920216</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920328</v>
+        <v>23330051920191</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8205,22 +8058,22 @@
         <v>23330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8228,19 +8081,19 @@
         <v>23330051920357</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
         <v>84</v>
       </c>
-      <c r="D6" t="s">
-        <v>114</v>
-      </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8248,554 +8101,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920357</v>
+        <v>23330051920280</v>
       </c>
       <c r="B7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" t="s">
         <v>75</v>
       </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920280</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920280</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920213</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920226</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920215</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920227</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920237</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920242</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920240</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920244</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920333</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920252</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920239</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920256</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920257</v>
-      </c>
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920260</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920330</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>130</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920270</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>131</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920207</v>
-      </c>
-      <c r="B26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920327</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920276</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920278</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920277</v>
-      </c>
-      <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ARHV - Estadisticos 20232.xlsx
+++ b/grupos/2ARHV - Estadisticos 20232.xlsx
@@ -212,13 +212,13 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Miguel Lopez Yadira</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
@@ -2586,7 +2586,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2613,7 +2613,7 @@
         <v>5</v>
       </c>
       <c r="AK19">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -6085,7 +6085,7 @@
         <v>62.5</v>
       </c>
       <c r="AB19">
-        <v>58.9</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:28">
@@ -7755,28 +7755,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="G6" s="2">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7787,7 +7787,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -7808,7 +7808,7 @@
         <v>11.8</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7819,28 +7819,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>88.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>9.5</v>
       </c>
       <c r="I8">
         <v>0</v>
